--- a/Codelist Excel Files and Conversion Templates to XML/archingModel.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/archingModel.xlsx
@@ -1704,35 +1704,80 @@
         <f>IF(ISNA(VLOOKUP(B7,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B7" s="2" t="n"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>marston</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:archingModel</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
         <f>IF(ISNA(VLOOKUP(B8,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B8" s="2" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>hewlett_randolph</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:archingModel</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
         <f>IF(ISNA(VLOOKUP(B9,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B9" s="2" t="n"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>zaeske</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:archingModel</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
         <f>IF(ISNA(VLOOKUP(B10,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B10" s="20" t="n"/>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>adapted_terzaghi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:archingModel</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
         <f>IF(ISNA(VLOOKUP(B11,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B11" s="20" t="n"/>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>prandtl</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:archingModel</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12">

--- a/Codelist Excel Files and Conversion Templates to XML/archingModel.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/archingModel.xlsx
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:archingModel</t>
+          <t>//diggs:RIProgramBasis/diggs:archingModel</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:archingModel</t>
+          <t>//diggs:RIProgramBasis/diggs:archingModel</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:archingModel</t>
+          <t>//diggs:RIProgramBasis/diggs:archingModel</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:archingModel</t>
+          <t>//diggs:RIProgramBasis/diggs:archingModel</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:archingModel</t>
+          <t>//diggs:RIProgramBasis/diggs:archingModel</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/archingModel.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/archingModel.xlsx
@@ -1229,14 +1229,62 @@
         <f>IF(ISNA(VLOOKUP(B7,AssociatedElements!B$2:B2945,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="G7" s="9" t="n"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>concentric_arches</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Concentric Arches (CUR 226 / Van Eekelen)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The Concentric Arches model of CUR 226, in which embankment load reaches the inclusion heads through a system of concentric hemispherical and two-dimensional arches. Ranked among the more accurate methods by Han et al. (2025). The governing document itself is registered separately as cur226 in the DIGGS rigid inclusions specification registry.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>CUR 226 (CROW/CUR)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2">
         <f>IF(ISNA(VLOOKUP(B8,AssociatedElements!B$2:B2946,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="G8" s="9" t="n"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fhwa_parabolic</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FHWA generalized parabolic arching (GEC-13)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>The generalized parabolic arching formulation of FHWA GEC-13 (Eq 3-23 and Eq 3-25), which yields the stress reduction ratio applied to the soft soil between inclusion heads.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>FHWA GEC-13 (FHWA-NHI-16-028)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2">
@@ -1784,28 +1832,64 @@
         <f>IF(ISNA(VLOOKUP(B12,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B12" s="20" t="n"/>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>concentric_arches</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>//diggs:ArchingCoefficients/diggs:archingModel</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
         <f>IF(ISNA(VLOOKUP(B13,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B13" s="20" t="n"/>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>concentric_arches</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>//diggs:RIProgramBasis/diggs:archingModel</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
         <f>IF(ISNA(VLOOKUP(B14,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B14" s="20" t="n"/>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>fhwa_parabolic</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>//diggs:ArchingCoefficients/diggs:archingModel</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
         <f>IF(ISNA(VLOOKUP(B15,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>fhwa_parabolic</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>//diggs:RIProgramBasis/diggs:archingModel</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
